--- a/sources/prototype_step6b.xlsx
+++ b/sources/prototype_step6b.xlsx
@@ -5198,7 +5198,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">

--- a/sources/prototype_step6b.xlsx
+++ b/sources/prototype_step6b.xlsx
@@ -728,6 +728,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>1600af09-1140-4ea9-8457-fe29c60319dd</t>
@@ -790,6 +795,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>e4342249-4607-45e4-aa42-9ee5e753c232</t>
@@ -842,6 +852,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>fad1d0df-58a4-409d-a250-80c77b202264</t>
@@ -892,6 +907,11 @@
       <c r="O9" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>c4222188-365d-401c-a75a-8d64d256a8cc</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -5648,6 +5668,11 @@
       <c r="K99" t="inlineStr">
         <is>
           <t>sLLmmmmmmm</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>4e36f2e9-e904-45da-b205-e22a2d153bbd</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">

--- a/sources/prototype_step6b.xlsx
+++ b/sources/prototype_step6b.xlsx
@@ -2706,7 +2706,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2892,7 +2892,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3943,7 +3943,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4072,7 +4072,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4687,6 +4687,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
@@ -4804,6 +4809,11 @@
       <c r="A81" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
